--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/46.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/46.xlsx
@@ -426,13 +426,13 @@
         <v>-13.61439116145311</v>
       </c>
       <c r="E2">
-        <v>-17.60502109387665</v>
+        <v>-18.373493938521</v>
       </c>
       <c r="F2">
-        <v>-0.2324905708846198</v>
+        <v>0.4872066258112299</v>
       </c>
       <c r="G2">
-        <v>-14.83787001991219</v>
+        <v>-14.26109910335426</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.39460273196214</v>
       </c>
       <c r="E3">
-        <v>-18.49873402602121</v>
+        <v>-18.07972899509323</v>
       </c>
       <c r="F3">
-        <v>0.4421616631817983</v>
+        <v>0.462912266621926</v>
       </c>
       <c r="G3">
-        <v>-14.75579082071217</v>
+        <v>-14.53113624864688</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.10000057183735</v>
       </c>
       <c r="E4">
-        <v>-18.6080133224001</v>
+        <v>-18.51862375505581</v>
       </c>
       <c r="F4">
-        <v>0.6795626487827059</v>
+        <v>0.3709469175631249</v>
       </c>
       <c r="G4">
-        <v>-13.96507069028481</v>
+        <v>-14.366523580688</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.75382630337976</v>
       </c>
       <c r="E5">
-        <v>-20.53552700467567</v>
+        <v>-18.76971445212097</v>
       </c>
       <c r="F5">
-        <v>-0.03369399135637764</v>
+        <v>0.6154080785380925</v>
       </c>
       <c r="G5">
-        <v>-13.93502102004109</v>
+        <v>-13.75145695709533</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.36528775510749</v>
       </c>
       <c r="E6">
-        <v>-19.42133669614127</v>
+        <v>-19.16183989935466</v>
       </c>
       <c r="F6">
-        <v>0.196819119290252</v>
+        <v>0.6665266309648501</v>
       </c>
       <c r="G6">
-        <v>-14.68943352543985</v>
+        <v>-13.63931372855635</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.93272355166689</v>
       </c>
       <c r="E7">
-        <v>-20.40419830937327</v>
+        <v>-19.8323717145369</v>
       </c>
       <c r="F7">
-        <v>1.007489280896349</v>
+        <v>0.922278439639975</v>
       </c>
       <c r="G7">
-        <v>-13.56025646622055</v>
+        <v>-12.73591386157653</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.4679583494634</v>
       </c>
       <c r="E8">
-        <v>-21.12761711756588</v>
+        <v>-20.72265409412715</v>
       </c>
       <c r="F8">
-        <v>0.9007160361451039</v>
+        <v>0.9879679746819758</v>
       </c>
       <c r="G8">
-        <v>-12.52878260720679</v>
+        <v>-12.8019957232945</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.97644611260883</v>
       </c>
       <c r="E9">
-        <v>-20.68069835332373</v>
+        <v>-20.93610423695538</v>
       </c>
       <c r="F9">
-        <v>0.8579871887738998</v>
+        <v>1.07373216536342</v>
       </c>
       <c r="G9">
-        <v>-13.05296137934904</v>
+        <v>-12.44527794146003</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.44574449114441</v>
       </c>
       <c r="E10">
-        <v>-20.49595936038403</v>
+        <v>-21.52244630537203</v>
       </c>
       <c r="F10">
-        <v>1.170820138441133</v>
+        <v>1.275850498176888</v>
       </c>
       <c r="G10">
-        <v>-13.13966029110302</v>
+        <v>-12.5376500012105</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.885039065167348</v>
       </c>
       <c r="E11">
-        <v>-22.06471034199827</v>
+        <v>-22.20211518546889</v>
       </c>
       <c r="F11">
-        <v>1.15485252838477</v>
+        <v>1.528928336875776</v>
       </c>
       <c r="G11">
-        <v>-13.70267649978267</v>
+        <v>-12.23036797358106</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.29203063417507</v>
       </c>
       <c r="E12">
-        <v>-22.40762438824406</v>
+        <v>-22.21567126723313</v>
       </c>
       <c r="F12">
-        <v>1.244549807494706</v>
+        <v>1.599800138389691</v>
       </c>
       <c r="G12">
-        <v>-12.70313074174592</v>
+        <v>-11.66142668005188</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.656744153641334</v>
       </c>
       <c r="E13">
-        <v>-23.27654680199072</v>
+        <v>-24.26749887088348</v>
       </c>
       <c r="F13">
-        <v>1.159088799282686</v>
+        <v>1.827496799866802</v>
       </c>
       <c r="G13">
-        <v>-11.56615799917757</v>
+        <v>-11.17860340760516</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.995601110995285</v>
       </c>
       <c r="E14">
-        <v>-25.15957959097738</v>
+        <v>-24.08443777531901</v>
       </c>
       <c r="F14">
-        <v>1.010748078258962</v>
+        <v>2.160349732924894</v>
       </c>
       <c r="G14">
-        <v>-12.15037867542624</v>
+        <v>-11.35579594837632</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.312410787784522</v>
       </c>
       <c r="E15">
-        <v>-23.90159264674343</v>
+        <v>-25.06118170826954</v>
       </c>
       <c r="F15">
-        <v>2.274364565511412</v>
+        <v>2.46878073821365</v>
       </c>
       <c r="G15">
-        <v>-11.64526094954371</v>
+        <v>-10.75216699683731</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.61074748742963</v>
       </c>
       <c r="E16">
-        <v>-26.01711389927135</v>
+        <v>-25.90105240879901</v>
       </c>
       <c r="F16">
-        <v>1.876194862742579</v>
+        <v>2.736376544014003</v>
       </c>
       <c r="G16">
-        <v>-10.61662627527278</v>
+        <v>-10.26747965275254</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.912322400632426</v>
       </c>
       <c r="E17">
-        <v>-27.46606134700958</v>
+        <v>-26.51138757903919</v>
       </c>
       <c r="F17">
-        <v>2.688084381165597</v>
+        <v>2.866899082203509</v>
       </c>
       <c r="G17">
-        <v>-9.668483467490463</v>
+        <v>-10.32338744279893</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.225061051784214</v>
       </c>
       <c r="E18">
-        <v>-26.96846094497055</v>
+        <v>-27.3725061087065</v>
       </c>
       <c r="F18">
-        <v>1.844839499811812</v>
+        <v>3.010337524937466</v>
       </c>
       <c r="G18">
-        <v>-10.27151847463499</v>
+        <v>-9.878778944304637</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.558028207123678</v>
       </c>
       <c r="E19">
-        <v>-27.73697947493947</v>
+        <v>-27.74454662597331</v>
       </c>
       <c r="F19">
-        <v>2.906027844842147</v>
+        <v>3.515298696540406</v>
       </c>
       <c r="G19">
-        <v>-8.765983002022283</v>
+        <v>-9.444608202685611</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.930491425993028</v>
       </c>
       <c r="E20">
-        <v>-29.4088214680586</v>
+        <v>-29.3522401935748</v>
       </c>
       <c r="F20">
-        <v>2.774663685371396</v>
+        <v>3.547157706852075</v>
       </c>
       <c r="G20">
-        <v>-9.811688029802207</v>
+        <v>-8.831136744038107</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.349006073370829</v>
       </c>
       <c r="E21">
-        <v>-29.52885342855747</v>
+        <v>-29.40970610207079</v>
       </c>
       <c r="F21">
-        <v>2.917933141155181</v>
+        <v>3.787399164277182</v>
       </c>
       <c r="G21">
-        <v>-8.445771261805353</v>
+        <v>-8.753029792733475</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.823837454298142</v>
       </c>
       <c r="E22">
-        <v>-29.95162749876273</v>
+        <v>-30.37757462242016</v>
       </c>
       <c r="F22">
-        <v>3.729193100352072</v>
+        <v>4.099867632287183</v>
       </c>
       <c r="G22">
-        <v>-9.157140421130423</v>
+        <v>-8.06312878618113</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.372034845013038</v>
       </c>
       <c r="E23">
-        <v>-30.08018600211147</v>
+        <v>-31.20322265076776</v>
       </c>
       <c r="F23">
-        <v>3.317519352182801</v>
+        <v>3.654966410856819</v>
       </c>
       <c r="G23">
-        <v>-9.364924361647947</v>
+        <v>-7.780622724721352</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.999958970934201</v>
       </c>
       <c r="E24">
-        <v>-31.83522512448957</v>
+        <v>-31.45926397573212</v>
       </c>
       <c r="F24">
-        <v>3.01899065082711</v>
+        <v>3.751182941426788</v>
       </c>
       <c r="G24">
-        <v>-7.491485372000146</v>
+        <v>-8.123027099335042</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.715985853214951</v>
       </c>
       <c r="E25">
-        <v>-30.64098374427476</v>
+        <v>-30.31202656468605</v>
       </c>
       <c r="F25">
-        <v>3.494377449415301</v>
+        <v>3.76422972802088</v>
       </c>
       <c r="G25">
-        <v>-7.479582987409261</v>
+        <v>-8.128473112552104</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.529208035905963</v>
       </c>
       <c r="E26">
-        <v>-30.41413534171263</v>
+        <v>-31.67538255683656</v>
       </c>
       <c r="F26">
-        <v>3.775028325483774</v>
+        <v>3.670039384118159</v>
       </c>
       <c r="G26">
-        <v>-7.637106178430968</v>
+        <v>-7.266893457805035</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.436779640667154</v>
       </c>
       <c r="E27">
-        <v>-31.11019279369727</v>
+        <v>-32.03586676359204</v>
       </c>
       <c r="F27">
-        <v>3.67903214064295</v>
+        <v>4.19101786782163</v>
       </c>
       <c r="G27">
-        <v>-8.222444253364635</v>
+        <v>-7.048024295753644</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.436183253025304</v>
       </c>
       <c r="E28">
-        <v>-31.79537506182784</v>
+        <v>-32.35652167374241</v>
       </c>
       <c r="F28">
-        <v>3.202488941160451</v>
+        <v>3.808467860799984</v>
       </c>
       <c r="G28">
-        <v>-7.230870403936854</v>
+        <v>-6.632177065047347</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.521897098269368</v>
       </c>
       <c r="E29">
-        <v>-30.65960674385529</v>
+        <v>-31.75616044049881</v>
       </c>
       <c r="F29">
-        <v>3.237398000249228</v>
+        <v>3.421880391057095</v>
       </c>
       <c r="G29">
-        <v>-6.903634455397532</v>
+        <v>-6.962109912749288</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.677610219073961</v>
       </c>
       <c r="E30">
-        <v>-31.72738283922907</v>
+        <v>-31.79729384545991</v>
       </c>
       <c r="F30">
-        <v>2.888340544057572</v>
+        <v>3.622119986601013</v>
       </c>
       <c r="G30">
-        <v>-7.211710149382673</v>
+        <v>-7.024632024217269</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.889373170983876</v>
       </c>
       <c r="E31">
-        <v>-32.10837560350656</v>
+        <v>-31.43940747238811</v>
       </c>
       <c r="F31">
-        <v>3.255709890055514</v>
+        <v>3.470228882888891</v>
       </c>
       <c r="G31">
-        <v>-6.574257696293498</v>
+        <v>-6.68900514256211</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.143031814839617</v>
       </c>
       <c r="E32">
-        <v>-31.2264474084962</v>
+        <v>-30.56840637637338</v>
       </c>
       <c r="F32">
-        <v>3.092972143571134</v>
+        <v>3.480161008048456</v>
       </c>
       <c r="G32">
-        <v>-7.759865999849706</v>
+        <v>-6.514056536767017</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.41876249748003</v>
       </c>
       <c r="E33">
-        <v>-30.83310922355567</v>
+        <v>-31.30889488311104</v>
       </c>
       <c r="F33">
-        <v>2.819163582249785</v>
+        <v>3.353394287663242</v>
       </c>
       <c r="G33">
-        <v>-8.107572796727947</v>
+        <v>-6.494784020195419</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.702763399365758</v>
       </c>
       <c r="E34">
-        <v>-29.62194143058652</v>
+        <v>-30.97242869744704</v>
       </c>
       <c r="F34">
-        <v>3.118933177974871</v>
+        <v>3.425661059883471</v>
       </c>
       <c r="G34">
-        <v>-7.269044711348112</v>
+        <v>-6.616575255370853</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.984280452859215</v>
       </c>
       <c r="E35">
-        <v>-29.68942280819233</v>
+        <v>-30.64964526649269</v>
       </c>
       <c r="F35">
-        <v>2.562099639608626</v>
+        <v>3.579555155975564</v>
       </c>
       <c r="G35">
-        <v>-7.961790124132476</v>
+        <v>-6.374339929228998</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.250093087833948</v>
       </c>
       <c r="E36">
-        <v>-28.48802336825918</v>
+        <v>-30.07593103710919</v>
       </c>
       <c r="F36">
-        <v>2.678440527862205</v>
+        <v>3.380481901734786</v>
       </c>
       <c r="G36">
-        <v>-7.701266532129872</v>
+        <v>-6.775488667887328</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.495879394721611</v>
       </c>
       <c r="E37">
-        <v>-29.79878101558639</v>
+        <v>-29.42449984080983</v>
       </c>
       <c r="F37">
-        <v>3.190770855880449</v>
+        <v>3.747009626451483</v>
       </c>
       <c r="G37">
-        <v>-8.032708390205478</v>
+        <v>-6.731385359509651</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.721387424540873</v>
       </c>
       <c r="E38">
-        <v>-30.14558454423789</v>
+        <v>-29.2398397588853</v>
       </c>
       <c r="F38">
-        <v>3.462342825214239</v>
+        <v>3.733502267581435</v>
       </c>
       <c r="G38">
-        <v>-7.652456051254418</v>
+        <v>-6.932655492272348</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.923520580180319</v>
       </c>
       <c r="E39">
-        <v>-27.71099283168002</v>
+        <v>-28.86314349172336</v>
       </c>
       <c r="F39">
-        <v>3.805076524652923</v>
+        <v>3.919798783001432</v>
       </c>
       <c r="G39">
-        <v>-8.378045936367283</v>
+        <v>-7.351170903950763</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.109233555682849</v>
       </c>
       <c r="E40">
-        <v>-29.00795143438049</v>
+        <v>-28.59537557458335</v>
       </c>
       <c r="F40">
-        <v>2.504862765544791</v>
+        <v>4.011078243850716</v>
       </c>
       <c r="G40">
-        <v>-8.970818106524145</v>
+        <v>-7.229588528342617</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.286440254032103</v>
       </c>
       <c r="E41">
-        <v>-26.87223934499692</v>
+        <v>-27.55461611887758</v>
       </c>
       <c r="F41">
-        <v>3.28288696780656</v>
+        <v>3.928693792172694</v>
       </c>
       <c r="G41">
-        <v>-8.806023991816188</v>
+        <v>-6.953760751546907</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.456599639548044</v>
       </c>
       <c r="E42">
-        <v>-25.99213648636383</v>
+        <v>-27.67981882747586</v>
       </c>
       <c r="F42">
-        <v>3.677272688279404</v>
+        <v>3.762965639364208</v>
       </c>
       <c r="G42">
-        <v>-8.171853244678042</v>
+        <v>-7.511159943238776</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.631581011175954</v>
       </c>
       <c r="E43">
-        <v>-25.82441735343328</v>
+        <v>-27.30423146773764</v>
       </c>
       <c r="F43">
-        <v>3.76291593732004</v>
+        <v>3.516514739887715</v>
       </c>
       <c r="G43">
-        <v>-9.224818753165852</v>
+        <v>-7.527892205323221</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.817661203887408</v>
       </c>
       <c r="E44">
-        <v>-24.3378251982468</v>
+        <v>-26.80347047188041</v>
       </c>
       <c r="F44">
-        <v>3.215900209411775</v>
+        <v>4.079206492526558</v>
       </c>
       <c r="G44">
-        <v>-7.643447677042782</v>
+        <v>-7.590978237622883</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.012159472452831</v>
       </c>
       <c r="E45">
-        <v>-25.06107787798642</v>
+        <v>-26.39356928017646</v>
       </c>
       <c r="F45">
-        <v>2.839866140380551</v>
+        <v>3.87820976917648</v>
       </c>
       <c r="G45">
-        <v>-8.150062664948315</v>
+        <v>-7.235984852590844</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.222136886458184</v>
       </c>
       <c r="E46">
-        <v>-26.01422741740059</v>
+        <v>-25.58429944068832</v>
       </c>
       <c r="F46">
-        <v>2.910383400646067</v>
+        <v>4.256369428963288</v>
       </c>
       <c r="G46">
-        <v>-8.016934271385971</v>
+        <v>-7.167254390485196</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.445554907794975</v>
       </c>
       <c r="E47">
-        <v>-25.0032817891901</v>
+        <v>-25.30424009463248</v>
       </c>
       <c r="F47">
-        <v>2.991301642021134</v>
+        <v>4.056492658341796</v>
       </c>
       <c r="G47">
-        <v>-8.565138420627939</v>
+        <v>-7.368837812598827</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.67441209358482</v>
       </c>
       <c r="E48">
-        <v>-23.15707552502069</v>
+        <v>-24.63023619478268</v>
       </c>
       <c r="F48">
-        <v>2.955267659999355</v>
+        <v>4.134722019127375</v>
       </c>
       <c r="G48">
-        <v>-8.108358630849871</v>
+        <v>-7.550945080062752</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.910794032786645</v>
       </c>
       <c r="E49">
-        <v>-23.67859427107942</v>
+        <v>-23.93236378944909</v>
       </c>
       <c r="F49">
-        <v>3.31776454893403</v>
+        <v>4.188014207619079</v>
       </c>
       <c r="G49">
-        <v>-7.878165364134526</v>
+        <v>-7.369459169811512</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.147779708229432</v>
       </c>
       <c r="E50">
-        <v>-22.91872688030011</v>
+        <v>-22.30327080049642</v>
       </c>
       <c r="F50">
-        <v>3.763701229617894</v>
+        <v>4.270181627037568</v>
       </c>
       <c r="G50">
-        <v>-7.874343234053137</v>
+        <v>-7.31704325065573</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.377088237164268</v>
       </c>
       <c r="E51">
-        <v>-22.23595970455492</v>
+        <v>-22.93539371734665</v>
       </c>
       <c r="F51">
-        <v>2.835152729858621</v>
+        <v>4.476242988688361</v>
       </c>
       <c r="G51">
-        <v>-9.294271086150944</v>
+        <v>-6.828108225121216</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.601064829037437</v>
       </c>
       <c r="E52">
-        <v>-21.12969372322829</v>
+        <v>-23.16714290927208</v>
       </c>
       <c r="F52">
-        <v>3.765669430566945</v>
+        <v>4.127806808048805</v>
       </c>
       <c r="G52">
-        <v>-8.06999112833887</v>
+        <v>-7.721292248516007</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.813389103365624</v>
       </c>
       <c r="E53">
-        <v>-21.94494003381286</v>
+        <v>-21.84506776108471</v>
       </c>
       <c r="F53">
-        <v>2.878555868295704</v>
+        <v>4.278975575385687</v>
       </c>
       <c r="G53">
-        <v>-8.742273525018089</v>
+        <v>-7.970340312668372</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.011421785073491</v>
       </c>
       <c r="E54">
-        <v>-20.87584529384345</v>
+        <v>-22.41933644418008</v>
       </c>
       <c r="F54">
-        <v>3.315390447957607</v>
+        <v>4.2578820278408</v>
       </c>
       <c r="G54">
-        <v>-8.68171860959951</v>
+        <v>-7.876037607292769</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.201191151390092</v>
       </c>
       <c r="E55">
-        <v>-20.64596920022551</v>
+        <v>-21.46163913836521</v>
       </c>
       <c r="F55">
-        <v>3.037903935367829</v>
+        <v>4.029577344690034</v>
       </c>
       <c r="G55">
-        <v>-8.117718150209013</v>
+        <v>-7.745108766048438</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.378617866148846</v>
       </c>
       <c r="E56">
-        <v>-20.99864329308465</v>
+        <v>-21.64524845782456</v>
       </c>
       <c r="F56">
-        <v>3.330859380837485</v>
+        <v>4.356084983442682</v>
       </c>
       <c r="G56">
-        <v>-8.603892313338424</v>
+        <v>-8.400536195647428</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.546278380537592</v>
       </c>
       <c r="E57">
-        <v>-21.32044241295502</v>
+        <v>-20.252132629926</v>
       </c>
       <c r="F57">
-        <v>3.372894056325143</v>
+        <v>4.171072437497023</v>
       </c>
       <c r="G57">
-        <v>-8.649562068470768</v>
+        <v>-8.566754471529837</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.711571516742088</v>
       </c>
       <c r="E58">
-        <v>-20.94871338653757</v>
+        <v>-20.80208010750317</v>
       </c>
       <c r="F58">
-        <v>3.142641053042992</v>
+        <v>4.419017711768165</v>
       </c>
       <c r="G58">
-        <v>-9.417948584293457</v>
+        <v>-8.697839957449636</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.870021383884661</v>
       </c>
       <c r="E59">
-        <v>-20.19462726592242</v>
+        <v>-20.10689067668542</v>
       </c>
       <c r="F59">
-        <v>2.710902589643112</v>
+        <v>4.355049524189182</v>
       </c>
       <c r="G59">
-        <v>-9.845093812217797</v>
+        <v>-8.455192133662385</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.027921074424473</v>
       </c>
       <c r="E60">
-        <v>-19.10075031397776</v>
+        <v>-19.84971967824071</v>
       </c>
       <c r="F60">
-        <v>3.083488993543885</v>
+        <v>4.001825379961445</v>
       </c>
       <c r="G60">
-        <v>-9.872819919775422</v>
+        <v>-8.525023024613187</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.192394850092603</v>
       </c>
       <c r="E61">
-        <v>-20.09418185003144</v>
+        <v>-19.22487318763158</v>
       </c>
       <c r="F61">
-        <v>3.293067603186966</v>
+        <v>4.061325353769728</v>
       </c>
       <c r="G61">
-        <v>-9.787511229516204</v>
+        <v>-8.999729492126134</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.356734401396277</v>
       </c>
       <c r="E62">
-        <v>-18.18249190290346</v>
+        <v>-18.95035422548306</v>
       </c>
       <c r="F62">
-        <v>3.183176383531583</v>
+        <v>4.534621353033254</v>
       </c>
       <c r="G62">
-        <v>-9.384241260877594</v>
+        <v>-9.282257744914936</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.529800566518137</v>
       </c>
       <c r="E63">
-        <v>-19.21490548045199</v>
+        <v>-18.78400980550103</v>
       </c>
       <c r="F63">
-        <v>3.35546189270063</v>
+        <v>4.434127133195228</v>
       </c>
       <c r="G63">
-        <v>-9.738004985207217</v>
+        <v>-9.996622733658308</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.715782134164062</v>
       </c>
       <c r="E64">
-        <v>-18.78545096983074</v>
+        <v>-19.0936815483029</v>
       </c>
       <c r="F64">
-        <v>3.299765782006002</v>
+        <v>4.051436303715107</v>
       </c>
       <c r="G64">
-        <v>-10.4872403840818</v>
+        <v>-9.963586371602361</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.904274907451779</v>
       </c>
       <c r="E65">
-        <v>-19.60871297827223</v>
+        <v>-18.31562309192084</v>
       </c>
       <c r="F65">
-        <v>3.337209645347346</v>
+        <v>4.391182910299297</v>
       </c>
       <c r="G65">
-        <v>-9.965095381976024</v>
+        <v>-10.01069464700441</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.10412559269723</v>
       </c>
       <c r="E66">
-        <v>-17.53834543926786</v>
+        <v>-18.23829029705253</v>
       </c>
       <c r="F66">
-        <v>3.080831590915704</v>
+        <v>4.42218207524686</v>
       </c>
       <c r="G66">
-        <v>-10.32097380942445</v>
+        <v>-10.36114272570332</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.315252844747206</v>
       </c>
       <c r="E67">
-        <v>-16.84033597796055</v>
+        <v>-18.51571235391711</v>
       </c>
       <c r="F67">
-        <v>3.25373506216724</v>
+        <v>4.590405270672578</v>
       </c>
       <c r="G67">
-        <v>-10.76773095071723</v>
+        <v>-10.19443101909319</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.523780437483119</v>
       </c>
       <c r="E68">
-        <v>-18.56284714924259</v>
+        <v>-17.24240005989455</v>
       </c>
       <c r="F68">
-        <v>2.633327639105744</v>
+        <v>4.128129871335897</v>
       </c>
       <c r="G68">
-        <v>-10.81919003198037</v>
+        <v>-10.16591907741364</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.737133761159129</v>
       </c>
       <c r="E69">
-        <v>-19.04457813080945</v>
+        <v>-17.77325107180016</v>
       </c>
       <c r="F69">
-        <v>2.438233861868016</v>
+        <v>4.341104787330456</v>
       </c>
       <c r="G69">
-        <v>-10.56647909316667</v>
+        <v>-10.22100578828613</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.94922896505182</v>
       </c>
       <c r="E70">
-        <v>-17.12804138606539</v>
+        <v>-18.4559601025868</v>
       </c>
       <c r="F70">
-        <v>2.917767467674622</v>
+        <v>4.355158868686352</v>
       </c>
       <c r="G70">
-        <v>-9.834648223108754</v>
+        <v>-10.0600220553089</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.14568296900814</v>
       </c>
       <c r="E71">
-        <v>-18.52332934348684</v>
+        <v>-17.61398787712696</v>
       </c>
       <c r="F71">
-        <v>2.70524152681238</v>
+        <v>3.904430910944696</v>
       </c>
       <c r="G71">
-        <v>-10.72750851417425</v>
+        <v>-10.26310404481783</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.33217417068224</v>
       </c>
       <c r="E72">
-        <v>-17.78209741192204</v>
+        <v>-18.33546298241955</v>
       </c>
       <c r="F72">
-        <v>2.549440528959044</v>
+        <v>4.260864150490878</v>
       </c>
       <c r="G72">
-        <v>-10.55385483769635</v>
+        <v>-10.63727726498848</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.49997328691926</v>
       </c>
       <c r="E73">
-        <v>-17.41549760149075</v>
+        <v>-17.86903243137336</v>
       </c>
       <c r="F73">
-        <v>2.694885277542581</v>
+        <v>4.254112956158062</v>
       </c>
       <c r="G73">
-        <v>-10.07438376130462</v>
+        <v>-10.44448291454084</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.6380644535852</v>
       </c>
       <c r="E74">
-        <v>-15.73762929873929</v>
+        <v>-17.79687453781578</v>
       </c>
       <c r="F74">
-        <v>2.752763307976183</v>
+        <v>4.080213787288362</v>
       </c>
       <c r="G74">
-        <v>-10.08066390741854</v>
+        <v>-9.896832243152186</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.75151358325385</v>
       </c>
       <c r="E75">
-        <v>-16.43983765669601</v>
+        <v>-18.01564909756245</v>
       </c>
       <c r="F75">
-        <v>2.632075147592711</v>
+        <v>3.807178921121229</v>
       </c>
       <c r="G75">
-        <v>-9.210276905793352</v>
+        <v>-9.846912195825508</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.83105954813368</v>
       </c>
       <c r="E76">
-        <v>-17.24755834835998</v>
+        <v>-18.42071179807298</v>
       </c>
       <c r="F76">
-        <v>2.996197293371679</v>
+        <v>4.072804869237723</v>
       </c>
       <c r="G76">
-        <v>-9.80634644636879</v>
+        <v>-10.23269409182054</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.871494349425</v>
       </c>
       <c r="E77">
-        <v>-18.34263557837753</v>
+        <v>-18.79882015708537</v>
       </c>
       <c r="F77">
-        <v>2.872785460967803</v>
+        <v>4.011195872021913</v>
       </c>
       <c r="G77">
-        <v>-9.303172419834345</v>
+        <v>-10.152153926557</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.8791989418801</v>
       </c>
       <c r="E78">
-        <v>-16.84908679422196</v>
+        <v>-17.96310266788072</v>
       </c>
       <c r="F78">
-        <v>2.815351435462102</v>
+        <v>3.867445963144504</v>
       </c>
       <c r="G78">
-        <v>-9.575214616972939</v>
+        <v>-9.009923144382135</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.84590794383752</v>
       </c>
       <c r="E79">
-        <v>-19.19274394482271</v>
+        <v>-18.92889042935635</v>
       </c>
       <c r="F79">
-        <v>2.865681382121394</v>
+        <v>4.089648892006249</v>
       </c>
       <c r="G79">
-        <v>-9.661546719111874</v>
+        <v>-9.331637368111252</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.77231317133115</v>
       </c>
       <c r="E80">
-        <v>-20.47386012292462</v>
+        <v>-19.59598753877296</v>
       </c>
       <c r="F80">
-        <v>2.525886730227843</v>
+        <v>3.861934006446276</v>
       </c>
       <c r="G80">
-        <v>-9.442664503337527</v>
+        <v>-9.407488636089163</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.66410565305249</v>
       </c>
       <c r="E81">
-        <v>-20.49810241742764</v>
+        <v>-19.85139342240462</v>
       </c>
       <c r="F81">
-        <v>2.52155105524159</v>
+        <v>4.073195858651845</v>
       </c>
       <c r="G81">
-        <v>-8.734875980219169</v>
+        <v>-9.043835411248402</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.51268364482186</v>
       </c>
       <c r="E82">
-        <v>-20.53052653824058</v>
+        <v>-19.92568606658315</v>
       </c>
       <c r="F82">
-        <v>2.335630618622464</v>
+        <v>3.891972265206591</v>
       </c>
       <c r="G82">
-        <v>-8.271387882214237</v>
+        <v>-9.020085467703044</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.32337357815397</v>
       </c>
       <c r="E83">
-        <v>-21.14024703320468</v>
+        <v>-21.28184662011339</v>
       </c>
       <c r="F83">
-        <v>2.029827194735387</v>
+        <v>3.8975968798716</v>
       </c>
       <c r="G83">
-        <v>-8.762570758841699</v>
+        <v>-9.20401111877468</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.10113756760489</v>
       </c>
       <c r="E84">
-        <v>-22.11147965472716</v>
+        <v>-21.93349793661296</v>
       </c>
       <c r="F84">
-        <v>2.452165344848298</v>
+        <v>3.848209615316693</v>
       </c>
       <c r="G84">
-        <v>-8.507315649423962</v>
+        <v>-8.964788591890969</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.83794183646034</v>
       </c>
       <c r="E85">
-        <v>-21.90206643330666</v>
+        <v>-22.24586511356464</v>
       </c>
       <c r="F85">
-        <v>2.959603334985608</v>
+        <v>3.888335732308302</v>
       </c>
       <c r="G85">
-        <v>-8.183146020406902</v>
+        <v>-9.207463828496428</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.544322596628431</v>
       </c>
       <c r="E86">
-        <v>-24.42579021410667</v>
+        <v>-23.07439754717733</v>
       </c>
       <c r="F86">
-        <v>2.176365388290619</v>
+        <v>4.037847764839585</v>
       </c>
       <c r="G86">
-        <v>-7.968860020485211</v>
+        <v>-8.731458515549402</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.225943479950942</v>
       </c>
       <c r="E87">
-        <v>-24.05186829210971</v>
+        <v>-23.94770990529433</v>
       </c>
       <c r="F87">
-        <v>2.413440825502227</v>
+        <v>3.854218592456601</v>
       </c>
       <c r="G87">
-        <v>-7.692147201273113</v>
+        <v>-8.567710004050186</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.878173170014382</v>
       </c>
       <c r="E88">
-        <v>-25.71988102438734</v>
+        <v>-25.98937875404414</v>
       </c>
       <c r="F88">
-        <v>2.451698145633119</v>
+        <v>3.591306375951677</v>
       </c>
       <c r="G88">
-        <v>-7.973253903632054</v>
+        <v>-8.192880181614868</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.518896607551259</v>
       </c>
       <c r="E89">
-        <v>-27.31127946735587</v>
+        <v>-26.50881674122913</v>
       </c>
       <c r="F89">
-        <v>2.193020543291306</v>
+        <v>3.2179197691398</v>
       </c>
       <c r="G89">
-        <v>-7.429743873164909</v>
+        <v>-8.036927353464716</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.155658965188342</v>
       </c>
       <c r="E90">
-        <v>-28.10388246979748</v>
+        <v>-28.28601324602518</v>
       </c>
       <c r="F90">
-        <v>2.087743330069517</v>
+        <v>3.67423257991113</v>
       </c>
       <c r="G90">
-        <v>-7.996244120501398</v>
+        <v>-8.129694941020745</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.787945507904775</v>
       </c>
       <c r="E91">
-        <v>-30.40992190882359</v>
+        <v>-28.71880486194593</v>
       </c>
       <c r="F91">
-        <v>2.547737405578888</v>
+        <v>3.44294411737548</v>
       </c>
       <c r="G91">
-        <v>-7.945127046779695</v>
+        <v>-8.374337373675607</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.432892829068056</v>
       </c>
       <c r="E92">
-        <v>-31.06587595225568</v>
+        <v>-30.36790802306162</v>
       </c>
       <c r="F92">
-        <v>1.307171069676737</v>
+        <v>2.89361890114821</v>
       </c>
       <c r="G92">
-        <v>-7.324094871796327</v>
+        <v>-7.447251526392914</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.093031094451162</v>
       </c>
       <c r="E93">
-        <v>-32.09686913153112</v>
+        <v>-32.391070162148</v>
       </c>
       <c r="F93">
-        <v>1.703024657187343</v>
+        <v>3.204150646170467</v>
       </c>
       <c r="G93">
-        <v>-7.798213921776273</v>
+        <v>-7.766365448509282</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.764551287216125</v>
       </c>
       <c r="E94">
-        <v>-35.24759699622351</v>
+        <v>-35.0310568641696</v>
       </c>
       <c r="F94">
-        <v>2.17176132226586</v>
+        <v>2.893794515037604</v>
       </c>
       <c r="G94">
-        <v>-7.06551106302492</v>
+        <v>-7.774931301512725</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.457618841866875</v>
       </c>
       <c r="E95">
-        <v>-36.70433171519579</v>
+        <v>-36.25239171846193</v>
       </c>
       <c r="F95">
-        <v>1.739572226998857</v>
+        <v>2.189120589558926</v>
       </c>
       <c r="G95">
-        <v>-7.188090743066872</v>
+        <v>-7.506108152454972</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.165361250732681</v>
       </c>
       <c r="E96">
-        <v>-39.3851424079348</v>
+        <v>-37.8007753517392</v>
       </c>
       <c r="F96">
-        <v>1.088357820227248</v>
+        <v>1.932141140392852</v>
       </c>
       <c r="G96">
-        <v>-7.89772114649426</v>
+        <v>-7.403114278335553</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.883435884331251</v>
       </c>
       <c r="E97">
-        <v>-39.25125948766762</v>
+        <v>-40.08977208809388</v>
       </c>
       <c r="F97">
-        <v>0.9364352385538186</v>
+        <v>1.891807931550544</v>
       </c>
       <c r="G97">
-        <v>-6.844803936781386</v>
+        <v>-6.924849365944919</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.611002735911518</v>
       </c>
       <c r="E98">
-        <v>-42.22128320422239</v>
+        <v>-42.65013134599021</v>
       </c>
       <c r="F98">
-        <v>0.5136829047395076</v>
+        <v>1.422494722759679</v>
       </c>
       <c r="G98">
-        <v>-8.288415158437477</v>
+        <v>-7.990260293898566</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.345496928689283</v>
       </c>
       <c r="E99">
-        <v>-46.335310018504</v>
+        <v>-44.18665340772377</v>
       </c>
       <c r="F99">
-        <v>0.1168742096134745</v>
+        <v>1.394056869821572</v>
       </c>
       <c r="G99">
-        <v>-7.469445466161968</v>
+        <v>-7.193980582864423</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.072376860281924</v>
       </c>
       <c r="E100">
-        <v>-45.8545290840277</v>
+        <v>-46.17632197408107</v>
       </c>
       <c r="F100">
-        <v>0.1762490999439346</v>
+        <v>1.351041407328999</v>
       </c>
       <c r="G100">
-        <v>-7.502933487032178</v>
+        <v>-6.701173823101288</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.809203148637078</v>
       </c>
       <c r="E101">
-        <v>-48.7480766055499</v>
+        <v>-48.32129572471901</v>
       </c>
       <c r="F101">
-        <v>0.007848633894017564</v>
+        <v>0.509376222612353</v>
       </c>
       <c r="G101">
-        <v>-7.646895165275347</v>
+        <v>-7.516723439962439</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.522675958518118</v>
       </c>
       <c r="E102">
-        <v>-50.11562422622998</v>
+        <v>-50.25480249093631</v>
       </c>
       <c r="F102">
-        <v>-0.662409939467952</v>
+        <v>0.5760987318056449</v>
       </c>
       <c r="G102">
-        <v>-7.17155428682676</v>
+        <v>-7.288124032819968</v>
       </c>
     </row>
   </sheetData>
